--- a/Dars materiallari 2025-2026/Sun'iy intellekt asoslari 2025-2026/5.2 NumPy va Pandas bilan ma’lumotlarni qayta ishlash/data.xlsx
+++ b/Dars materiallari 2025-2026/Sun'iy intellekt asoslari 2025-2026/5.2 NumPy va Pandas bilan ma’lumotlarni qayta ishlash/data.xlsx
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Veli</t>
+          <t>Vali</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -478,7 +478,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sami</t>
+          <t>G'ani</t>
         </is>
       </c>
       <c r="B4" t="n">
